--- a/Front Limpieza/generated/gil_cuadrante_anual_2026.xlsx
+++ b/Front Limpieza/generated/gil_cuadrante_anual_2026.xlsx
@@ -75480,7 +75480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mínimo 10 descansos en junio/julio/agosto</t>
+          <t>minimo 10 descansos en junio/julio/agosto</t>
         </is>
       </c>
     </row>
